--- a/examples/excel-formatting.xlsx
+++ b/examples/excel-formatting.xlsx
@@ -5,19 +5,23 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Formatting" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="SecondSheet" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="DoNotTranslate" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="SecondSheet" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+  <si>
+    <t>Excel formatting translation sample</t>
+  </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>translate</t>
+    <t>source_text</t>
   </si>
   <si>
     <t>context</t>
@@ -29,6 +33,12 @@
     <t>link</t>
   </si>
   <si>
+    <t>hidden_text</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
     <t>안녕하세요</t>
   </si>
   <si>
@@ -36,6 +46,12 @@
   </si>
   <si>
     <t>OpenAI 문서</t>
+  </si>
+  <si>
+    <t>숨김 열 텍스트</t>
+  </si>
+  <si>
+    <t>ready</t>
   </si>
   <si>
     <t xml:space="preserve">줄바꿈이 있는 셀입니다.
@@ -48,6 +64,12 @@
     <t>일반 텍스트 링크 아님</t>
   </si>
   <si>
+    <t>숨김 열 2</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
     <t>Preserve formatting</t>
   </si>
   <si>
@@ -57,18 +79,48 @@
     <t>https://example.com/plain-text</t>
   </si>
   <si>
-    <t>targetColumns=translate 로 이 열만 번역</t>
-  </si>
-  <si>
-    <t>context/link 열은 옵션에 따라 제외할 수 있습니다.</t>
+    <t>숨김 열 3</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>이 행은 숨김 처리되어 있습니다.</t>
+  </si>
+  <si>
+    <t>숨김 행은 기본 옵션에서 번역하지 않아야 합니다.</t>
+  </si>
+  <si>
+    <t>숨김 행 링크</t>
+  </si>
+  <si>
+    <t>숨김 행 열</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>targetColumns=source_text 로 이 열만 번역</t>
+  </si>
+  <si>
+    <t>context/link/status 열은 옵션으로 제외하거나 포함할 수 있습니다.</t>
   </si>
   <si>
     <t>번역하지 않아도 되는 링크 설명</t>
   </si>
   <si>
+    <t>숨김 열 5</t>
+  </si>
+  <si>
+    <t>keep</t>
+  </si>
+  <si>
     <t>병합 셀 예시: master 셀만 번역 대상으로 잡히고 나머지 병합 영역은 건드리지 않아야 합니다.</t>
   </si>
   <si>
+    <t>이 시트는 제외 옵션 확인용입니다.</t>
+  </si>
+  <si>
     <t>key</t>
   </si>
   <si>
@@ -81,7 +133,7 @@
     <t>두 번째 시트의 번역 대상</t>
   </si>
   <si>
-    <t>targetColumns=translate가 시트별 헤더에 적용되는지 확인합니다.</t>
+    <t>targetColumns=source_text가 시트별 헤더에 적용되는지 확인합니다.</t>
   </si>
   <si>
     <t>b</t>
@@ -97,13 +149,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <b/>
@@ -126,8 +183,11 @@
       <b/>
       <i/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -137,6 +197,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -180,18 +245,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,112 +600,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="24" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <f>A3+10</f>
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <f>A4+20</f>
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" hidden="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <f>A2+10</f>
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <f>A3+20</f>
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A7:E7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -645,45 +780,76 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>19</v>
+    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/examples/excel-formatting.xlsx
+++ b/examples/excel-formatting.xlsx
@@ -100,10 +100,10 @@
     <t>hidden</t>
   </si>
   <si>
-    <t>targetColumns=source_text 로 이 열만 번역</t>
-  </si>
-  <si>
-    <t>context/link/status 열은 옵션으로 제외하거나 포함할 수 있습니다.</t>
+    <t>번역 범위 Formatting!B:B 로 이 열만 번역</t>
+  </si>
+  <si>
+    <t>제외 범위로 context/link/status 열이나 특정 셀을 제외할 수 있습니다.</t>
   </si>
   <si>
     <t>번역하지 않아도 되는 링크 설명</t>
@@ -133,7 +133,7 @@
     <t>두 번째 시트의 번역 대상</t>
   </si>
   <si>
-    <t>targetColumns=source_text가 시트별 헤더에 적용되는지 확인합니다.</t>
+    <t>번역 범위 SecondSheet!B:B가 시트 지정 범위에 적용되는지 확인합니다.</t>
   </si>
   <si>
     <t>b</t>
@@ -774,7 +774,7 @@
     <hyperlink ref="E3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -805,7 +805,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -854,6 +854,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>